--- a/bin/testdata/Index.xlsx
+++ b/bin/testdata/Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\GameTabTool\bin\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8715F87C-F203-4069-B245-477C804FF3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1BEE0B-7560-4CF7-ABBD-D7ADD474F7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29460" yWindow="2055" windowWidth="20625" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29685" yWindow="1755" windowWidth="19455" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,55 +33,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+  <si>
+    <t>表类型</t>
+  </si>
+  <si>
+    <t>表文件名</t>
+  </si>
+  <si>
+    <t>game_type.xlsx</t>
+  </si>
+  <si>
+    <t>RuleData.xlsx</t>
+  </si>
+  <si>
+    <t>JewelsRoad.xlsx</t>
+  </si>
+  <si>
+    <t>##</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelsRoadData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
   <si>
     <t>模式</t>
-  </si>
-  <si>
-    <t>表类型</t>
-  </si>
-  <si>
-    <t>表文件名</t>
-  </si>
-  <si>
-    <t>类型表</t>
-  </si>
-  <si>
-    <t>game_type.xlsx</t>
-  </si>
-  <si>
-    <t>数据表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RuleData</t>
-  </si>
-  <si>
-    <t>RuleData.xlsx</t>
-  </si>
-  <si>
-    <t>JewelsRoadData</t>
-  </si>
-  <si>
-    <t>JewelsRoad.xlsx</t>
-  </si>
-  <si>
-    <t>##tag</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>##fileType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>##dataname</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>##filename</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>##var</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>group</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tableFileName</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tableType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>类名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>取值c|s|e，可以有多个，以'|'分隔。空则表示属于所有分组</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +136,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -171,7 +191,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -186,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,31 +485,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -495,58 +520,63 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C14" s="2"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C20" s="2"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/bin/testdata/Index.xlsx
+++ b/bin/testdata/Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\GameTabTool\bin\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1BEE0B-7560-4CF7-ABBD-D7ADD474F7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3842BA16-EA0F-4ED9-9DAB-806791D8033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29685" yWindow="1755" windowWidth="19455" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16575" yWindow="4530" windowWidth="22935" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>表类型</t>
   </si>
@@ -44,20 +44,10 @@
     <t>game_type.xlsx</t>
   </si>
   <si>
-    <t>RuleData.xlsx</t>
-  </si>
-  <si>
-    <t>JewelsRoad.xlsx</t>
-  </si>
-  <si>
     <t>##</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>JewelsRoadData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>模式</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -70,10 +60,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>RuleData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>##var</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -90,11 +76,35 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>类名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>取值c|s|e，可以有多个，以'|'分隔。空则表示属于所有分组</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>类名,纯结构体不用定义</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>data\config\GameConfig.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>data\GameItem.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>data\Hero.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameConfigData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameItemData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeroData</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -489,29 +499,29 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -520,27 +530,27 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -550,18 +560,26 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">

--- a/bin/testdata/Index.xlsx
+++ b/bin/testdata/Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\project\GameTabTool\bin\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3842BA16-EA0F-4ED9-9DAB-806791D8033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE31760E-FFF9-4565-8434-BE1557F58624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16575" yWindow="4530" windowWidth="22935" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16575" yWindow="1995" windowWidth="22935" windowHeight="13530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>表类型</t>
   </si>
@@ -105,6 +105,14 @@
   </si>
   <si>
     <t>HeroData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_enum_type.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_class_type.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -582,6 +590,16 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
     </row>
